--- a/tpl/tpl-samples.xlsx
+++ b/tpl/tpl-samples.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20752" windowHeight="9555" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="25520" windowHeight="14260" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet2" sheetId="1" state="visible" r:id="rId1"/>
@@ -784,7 +784,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -840,9 +840,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1460,13 +1457,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9.026548672566371" defaultRowHeight="13.5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.02884615384615" defaultRowHeight="16.8"/>
   <cols>
-    <col width="13.4336283185841" customWidth="1" style="1" min="1" max="1"/>
-    <col width="17.9911504424779" customWidth="1" style="2" min="2" max="2"/>
-    <col width="9.24778761061947" customWidth="1" style="1" min="3" max="5"/>
-    <col width="10.0796460176991" customWidth="1" style="3" min="6" max="7"/>
-    <col width="5.38053097345133" customWidth="1" style="3" min="8" max="9"/>
+    <col width="13.4326923076923" customWidth="1" style="1" min="1" max="1"/>
+    <col width="17.9903846153846" customWidth="1" style="2" min="2" max="2"/>
+    <col width="9.25" customWidth="1" style="1" min="3" max="5"/>
+    <col width="10.0769230769231" customWidth="1" style="3" min="6" max="7"/>
+    <col width="5.38461538461539" customWidth="1" style="3" min="8" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1504,7 +1501,7 @@
           <t>样地号</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>样地面积（平方米）</t>
         </is>
@@ -1535,12 +1532,17 @@
         </is>
       </c>
       <c r="H3" s="12" t="n"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="19.5" customHeight="1" s="3">
       <c r="A4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="23" t="n"/>
+      <c r="B4" s="11" t="n"/>
       <c r="C4" s="10" t="n"/>
       <c r="D4" s="10" t="n"/>
       <c r="E4" s="10">
@@ -1556,7 +1558,7 @@
       <c r="A5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="23" t="n"/>
+      <c r="B5" s="11" t="n"/>
       <c r="C5" s="10" t="n"/>
       <c r="D5" s="10" t="n"/>
       <c r="E5" s="10">
@@ -1571,7 +1573,7 @@
       <c r="A6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="23" t="n"/>
+      <c r="B6" s="11" t="n"/>
       <c r="C6" s="10" t="n"/>
       <c r="D6" s="10" t="n"/>
       <c r="E6" s="10">
@@ -1586,7 +1588,7 @@
       <c r="A7" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="23" t="n"/>
+      <c r="B7" s="11" t="n"/>
       <c r="C7" s="10" t="n"/>
       <c r="D7" s="10" t="n"/>
       <c r="E7" s="10">
@@ -1601,7 +1603,7 @@
       <c r="A8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="23" t="n"/>
+      <c r="B8" s="11" t="n"/>
       <c r="C8" s="10" t="n"/>
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="10" t="n"/>
@@ -1613,7 +1615,7 @@
       <c r="A9" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="23" t="n"/>
+      <c r="B9" s="11" t="n"/>
       <c r="C9" s="10" t="n"/>
       <c r="D9" s="10" t="n"/>
       <c r="E9" s="10" t="n"/>
@@ -1625,7 +1627,7 @@
       <c r="A10" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="23" t="n"/>
+      <c r="B10" s="11" t="n"/>
       <c r="C10" s="10" t="n"/>
       <c r="D10" s="10" t="n"/>
       <c r="E10" s="10" t="n"/>
@@ -1637,7 +1639,7 @@
       <c r="A11" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="23" t="n"/>
+      <c r="B11" s="11" t="n"/>
       <c r="C11" s="10" t="n"/>
       <c r="D11" s="10" t="n"/>
       <c r="E11" s="10" t="n"/>
@@ -1649,7 +1651,7 @@
       <c r="A12" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="23" t="n"/>
+      <c r="B12" s="11" t="n"/>
       <c r="C12" s="10" t="n"/>
       <c r="D12" s="10" t="n"/>
       <c r="E12" s="10" t="n"/>
@@ -1661,7 +1663,7 @@
       <c r="A13" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="23" t="n"/>
+      <c r="B13" s="11" t="n"/>
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
       <c r="E13" s="10" t="n"/>
@@ -1673,7 +1675,7 @@
       <c r="A14" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="23" t="n"/>
+      <c r="B14" s="11" t="n"/>
       <c r="C14" s="10" t="n"/>
       <c r="D14" s="10" t="n"/>
       <c r="E14" s="10" t="n"/>
@@ -1685,7 +1687,7 @@
       <c r="A15" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="23" t="n"/>
+      <c r="B15" s="11" t="n"/>
       <c r="C15" s="10" t="n"/>
       <c r="D15" s="10" t="n"/>
       <c r="E15" s="10" t="n"/>
@@ -1697,7 +1699,7 @@
       <c r="A16" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="23" t="n"/>
+      <c r="B16" s="11" t="n"/>
       <c r="C16" s="10" t="n"/>
       <c r="D16" s="10" t="n"/>
       <c r="E16" s="10" t="n"/>
@@ -1709,7 +1711,7 @@
       <c r="A17" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="23" t="n"/>
+      <c r="B17" s="11" t="n"/>
       <c r="C17" s="10" t="n"/>
       <c r="D17" s="10" t="n"/>
       <c r="E17" s="10" t="n"/>
@@ -1721,7 +1723,7 @@
       <c r="A18" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="23" t="n"/>
+      <c r="B18" s="11" t="n"/>
       <c r="C18" s="10" t="n"/>
       <c r="D18" s="10" t="n"/>
       <c r="E18" s="10" t="n"/>
@@ -1733,7 +1735,7 @@
       <c r="A19" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="B19" s="23" t="n"/>
+      <c r="B19" s="11" t="n"/>
       <c r="C19" s="10" t="n"/>
       <c r="D19" s="10" t="n"/>
       <c r="E19" s="10" t="n"/>
@@ -1745,7 +1747,7 @@
       <c r="A20" s="10" t="n">
         <v>17</v>
       </c>
-      <c r="B20" s="23" t="n"/>
+      <c r="B20" s="11" t="n"/>
       <c r="C20" s="10" t="n"/>
       <c r="D20" s="10" t="n"/>
       <c r="E20" s="10" t="n"/>
@@ -1757,7 +1759,7 @@
       <c r="A21" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="B21" s="23" t="n"/>
+      <c r="B21" s="11" t="n"/>
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
       <c r="E21" s="10" t="n"/>
@@ -1769,7 +1771,7 @@
       <c r="A22" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B22" s="23" t="n"/>
+      <c r="B22" s="11" t="n"/>
       <c r="C22" s="10" t="n"/>
       <c r="D22" s="10" t="n"/>
       <c r="E22" s="10" t="n"/>
@@ -1781,7 +1783,7 @@
       <c r="A23" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="B23" s="23" t="n"/>
+      <c r="B23" s="11" t="n"/>
       <c r="C23" s="10" t="n"/>
       <c r="D23" s="10" t="n"/>
       <c r="E23" s="10" t="n"/>
@@ -1793,7 +1795,7 @@
       <c r="A24" s="10" t="n">
         <v>21</v>
       </c>
-      <c r="B24" s="23" t="n"/>
+      <c r="B24" s="11" t="n"/>
       <c r="C24" s="10" t="n"/>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1805,7 +1807,7 @@
       <c r="A25" s="10" t="n">
         <v>22</v>
       </c>
-      <c r="B25" s="23" t="n"/>
+      <c r="B25" s="11" t="n"/>
       <c r="C25" s="10" t="n"/>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1867,7 +1869,7 @@
           <t>样地总株数</t>
         </is>
       </c>
-      <c r="B29" s="23">
+      <c r="B29" s="11">
         <f>SUM(C4:C26)</f>
         <v/>
       </c>
@@ -1889,7 +1891,7 @@
           <t>样地成活株数</t>
         </is>
       </c>
-      <c r="B30" s="23">
+      <c r="B30" s="11">
         <f>SUM(D4:D26)</f>
         <v/>
       </c>
@@ -1933,7 +1935,7 @@
           <t>单个网格面积</t>
         </is>
       </c>
-      <c r="B32" s="23" t="n"/>
+      <c r="B32" s="11" t="n"/>
       <c r="C32" s="19" t="n"/>
       <c r="D32" s="19" t="n"/>
       <c r="E32" s="19" t="n"/>
@@ -1952,7 +1954,7 @@
           <t>种植网格数量</t>
         </is>
       </c>
-      <c r="B33" s="23" t="n"/>
+      <c r="B33" s="11" t="n"/>
       <c r="C33" s="19" t="n"/>
       <c r="D33" s="19" t="n"/>
       <c r="E33" s="19" t="n"/>
@@ -1971,7 +1973,7 @@
           <t>调查总株数</t>
         </is>
       </c>
-      <c r="B34" s="23">
+      <c r="B34" s="11">
         <f>IF(OR(B27=0,B29=0),"",ROUND(B29/B27/150*B32*B33,0))</f>
         <v/>
       </c>
@@ -1993,7 +1995,7 @@
           <t>撑杆情况</t>
         </is>
       </c>
-      <c r="B35" s="23" t="n"/>
+      <c r="B35" s="11" t="n"/>
       <c r="C35" s="19" t="n"/>
       <c r="D35" s="19" t="n"/>
       <c r="E35" s="19" t="n"/>
@@ -2012,7 +2014,7 @@
           <t>覆膜情况</t>
         </is>
       </c>
-      <c r="B36" s="23" t="n"/>
+      <c r="B36" s="11" t="n"/>
       <c r="C36" s="19" t="n"/>
       <c r="D36" s="19" t="n"/>
       <c r="E36" s="19" t="n"/>
@@ -2031,7 +2033,7 @@
           <t>验收人</t>
         </is>
       </c>
-      <c r="B37" s="23" t="n"/>
+      <c r="B37" s="11" t="n"/>
       <c r="C37" s="19" t="n"/>
       <c r="D37" s="19" t="n"/>
       <c r="E37" s="19" t="n"/>
@@ -2050,7 +2052,7 @@
           <t>验收日期</t>
         </is>
       </c>
-      <c r="B38" s="23" t="n"/>
+      <c r="B38" s="11" t="n"/>
       <c r="C38" s="19" t="n"/>
       <c r="D38" s="19" t="n"/>
       <c r="E38" s="19" t="n"/>
@@ -2069,7 +2071,7 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="B39" s="23" t="n"/>
+      <c r="B39" s="11" t="n"/>
       <c r="C39" s="19" t="n"/>
       <c r="D39" s="19" t="n"/>
       <c r="E39" s="19" t="n"/>
